--- a/A/chrXIII:0-48653_26_finemapping.xlsx
+++ b/A/chrXIII:0-48653_26_finemapping.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2414" uniqueCount="2414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2406" uniqueCount="2406">
   <si>
     <t xml:space="preserve">DATA</t>
   </si>
@@ -6659,19 +6659,10 @@
     <t xml:space="preserve">in.hotspot</t>
   </si>
   <si>
-    <t xml:space="preserve">Beta.x</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SE.x</t>
-  </si>
-  <si>
     <t xml:space="preserve">bin_pos_l</t>
   </si>
   <si>
-    <t xml:space="preserve">Beta.y</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SE.y</t>
+    <t xml:space="preserve">SE</t>
   </si>
   <si>
     <t xml:space="preserve">chrom_short</t>
@@ -6939,21 +6930,6 @@
   </si>
   <si>
     <t xml:space="preserve">FMP52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_G1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_G2:M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_M:G1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_G1:S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_S</t>
   </si>
   <si>
     <t xml:space="preserve">cis_fdr</t>
@@ -7692,48 +7668,42 @@
         <v>2211</v>
       </c>
       <c r="Z1" t="s">
+        <v>122</v>
+      </c>
+      <c r="AA1" t="s">
         <v>2212</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>2213</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>2214</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE1" t="s">
         <v>2215</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AF1" t="s">
         <v>2216</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AG1" t="s">
         <v>2217</v>
       </c>
-      <c r="AF1" t="s">
-        <v>12</v>
-      </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>2218</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>2219</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>2220</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>2221</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>2222</v>
+        <v>2219</v>
       </c>
       <c r="B2" t="s">
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>2223</v>
+        <v>2220</v>
       </c>
       <c r="D2" t="s">
         <v>14</v>
@@ -7787,59 +7757,57 @@
         <v>23620</v>
       </c>
       <c r="U2" t="s">
-        <v>2224</v>
+        <v>2221</v>
       </c>
       <c r="V2" t="n">
         <v>302806</v>
       </c>
       <c r="W2" t="s">
-        <v>2225</v>
+        <v>2222</v>
       </c>
       <c r="X2" t="b">
         <v>1</v>
       </c>
-      <c r="Y2"/>
-      <c r="Z2"/>
-      <c r="AA2" t="s">
-        <v>2226</v>
-      </c>
-      <c r="AB2" t="n">
+      <c r="Y2" t="s">
+        <v>2223</v>
+      </c>
+      <c r="Z2" t="n">
         <v>-0.390261087711525</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AA2" t="n">
         <v>0.020149614005494</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>2224</v>
       </c>
       <c r="AD2" t="s">
         <v>18</v>
       </c>
       <c r="AE2" t="s">
-        <v>2227</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>2227</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>2228</v>
+        <v>2224</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>2225</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>2222</v>
+        <v>2219</v>
       </c>
       <c r="B3" t="s">
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>2229</v>
+        <v>2226</v>
       </c>
       <c r="D3" t="s">
         <v>14</v>
@@ -7893,59 +7861,57 @@
         <v>23620</v>
       </c>
       <c r="U3" t="s">
-        <v>2230</v>
+        <v>2227</v>
       </c>
       <c r="V3" t="n">
         <v>374534</v>
       </c>
       <c r="W3" t="s">
-        <v>2225</v>
+        <v>2222</v>
       </c>
       <c r="X3" t="b">
         <v>1</v>
       </c>
-      <c r="Y3"/>
-      <c r="Z3"/>
-      <c r="AA3" t="s">
-        <v>2226</v>
-      </c>
-      <c r="AB3" t="n">
+      <c r="Y3" t="s">
+        <v>2223</v>
+      </c>
+      <c r="Z3" t="n">
         <v>-1.13956033543993</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AA3" t="n">
         <v>0.0833831482769227</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>2228</v>
       </c>
       <c r="AD3" t="s">
         <v>18</v>
       </c>
       <c r="AE3" t="s">
-        <v>2231</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>2231</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>2232</v>
+        <v>2228</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>2229</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>2222</v>
+        <v>2219</v>
       </c>
       <c r="B4" t="s">
         <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>2233</v>
+        <v>2230</v>
       </c>
       <c r="D4" t="s">
         <v>14</v>
@@ -7999,59 +7965,57 @@
         <v>23620</v>
       </c>
       <c r="U4" t="s">
-        <v>2234</v>
+        <v>2231</v>
       </c>
       <c r="V4" t="n">
         <v>514457</v>
       </c>
       <c r="W4" t="s">
-        <v>2225</v>
+        <v>2222</v>
       </c>
       <c r="X4" t="b">
         <v>1</v>
       </c>
-      <c r="Y4"/>
-      <c r="Z4"/>
-      <c r="AA4" t="s">
-        <v>2226</v>
-      </c>
-      <c r="AB4" t="n">
+      <c r="Y4" t="s">
+        <v>2223</v>
+      </c>
+      <c r="Z4" t="n">
         <v>-0.760555055929974</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AA4" t="n">
         <v>0.0591936421250981</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>2232</v>
       </c>
       <c r="AD4" t="s">
         <v>18</v>
       </c>
       <c r="AE4" t="s">
-        <v>2235</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>2235</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI4" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>2236</v>
+        <v>2232</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>2233</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>2222</v>
+        <v>2219</v>
       </c>
       <c r="B5" t="s">
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>2237</v>
+        <v>2234</v>
       </c>
       <c r="D5" t="s">
         <v>14</v>
@@ -8105,27 +8069,31 @@
         <v>23620</v>
       </c>
       <c r="U5" t="s">
-        <v>2238</v>
+        <v>2235</v>
       </c>
       <c r="V5" t="n">
         <v>411173</v>
       </c>
       <c r="W5" t="s">
-        <v>2225</v>
+        <v>2222</v>
       </c>
       <c r="X5" t="b">
         <v>1</v>
       </c>
-      <c r="Y5"/>
-      <c r="Z5"/>
-      <c r="AA5" t="s">
-        <v>2226</v>
-      </c>
-      <c r="AB5" t="n">
+      <c r="Y5" t="s">
+        <v>2223</v>
+      </c>
+      <c r="Z5" t="n">
         <v>-0.644284926407286</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AA5" t="n">
         <v>0.0501477953150852</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>38</v>
       </c>
       <c r="AD5" t="s">
         <v>18</v>
@@ -8133,31 +8101,25 @@
       <c r="AE5" t="s">
         <v>38</v>
       </c>
-      <c r="AF5" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG5" t="s">
-        <v>38</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="s">
-        <v>2239</v>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>2236</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>2222</v>
+        <v>2219</v>
       </c>
       <c r="B6" t="s">
         <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>2240</v>
+        <v>2237</v>
       </c>
       <c r="D6" t="s">
         <v>14</v>
@@ -8211,59 +8173,57 @@
         <v>23620</v>
       </c>
       <c r="U6" t="s">
-        <v>2241</v>
+        <v>2238</v>
       </c>
       <c r="V6" t="n">
         <v>796551</v>
       </c>
       <c r="W6" t="s">
-        <v>2225</v>
+        <v>2222</v>
       </c>
       <c r="X6" t="b">
         <v>1</v>
       </c>
-      <c r="Y6"/>
-      <c r="Z6"/>
-      <c r="AA6" t="s">
-        <v>2226</v>
-      </c>
-      <c r="AB6" t="n">
+      <c r="Y6" t="s">
+        <v>2223</v>
+      </c>
+      <c r="Z6" t="n">
         <v>-1.45371417516148</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AA6" t="n">
         <v>0.120480966447533</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>2239</v>
       </c>
       <c r="AD6" t="s">
         <v>18</v>
       </c>
       <c r="AE6" t="s">
-        <v>2242</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG6" t="s">
-        <v>2242</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ6" t="s">
-        <v>2243</v>
+        <v>2239</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>2240</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>2222</v>
+        <v>2219</v>
       </c>
       <c r="B7" t="s">
         <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>2244</v>
+        <v>2241</v>
       </c>
       <c r="D7" t="s">
         <v>152</v>
@@ -8317,59 +8277,57 @@
         <v>32108</v>
       </c>
       <c r="U7" t="s">
-        <v>2230</v>
+        <v>2227</v>
       </c>
       <c r="V7" t="n">
         <v>552099</v>
       </c>
       <c r="W7" t="s">
-        <v>2225</v>
+        <v>2222</v>
       </c>
       <c r="X7" t="b">
         <v>1</v>
       </c>
-      <c r="Y7"/>
-      <c r="Z7"/>
-      <c r="AA7" t="s">
-        <v>2226</v>
-      </c>
-      <c r="AB7" t="n">
+      <c r="Y7" t="s">
+        <v>2223</v>
+      </c>
+      <c r="Z7" t="n">
         <v>-1.06847213306165</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AA7" t="n">
         <v>0.0939881347418463</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>2228</v>
       </c>
       <c r="AD7" t="s">
         <v>18</v>
       </c>
       <c r="AE7" t="s">
-        <v>2231</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG7" t="s">
-        <v>2231</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="s">
-        <v>2245</v>
+        <v>2228</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>2242</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>2222</v>
+        <v>2219</v>
       </c>
       <c r="B8" t="s">
         <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>2246</v>
+        <v>2243</v>
       </c>
       <c r="D8" t="s">
         <v>14</v>
@@ -8423,59 +8381,57 @@
         <v>23620</v>
       </c>
       <c r="U8" t="s">
-        <v>2247</v>
+        <v>2244</v>
       </c>
       <c r="V8" t="n">
         <v>1021706</v>
       </c>
       <c r="W8" t="s">
-        <v>2225</v>
+        <v>2222</v>
       </c>
       <c r="X8" t="b">
         <v>1</v>
       </c>
-      <c r="Y8"/>
-      <c r="Z8"/>
-      <c r="AA8" t="s">
-        <v>2226</v>
-      </c>
-      <c r="AB8" t="n">
+      <c r="Y8" t="s">
+        <v>2223</v>
+      </c>
+      <c r="Z8" t="n">
         <v>-0.918317592635161</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AA8" t="n">
         <v>0.0996530750870123</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>2245</v>
       </c>
       <c r="AD8" t="s">
         <v>18</v>
       </c>
       <c r="AE8" t="s">
-        <v>2248</v>
-      </c>
-      <c r="AF8" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG8" t="s">
-        <v>2248</v>
-      </c>
-      <c r="AH8" t="n">
+        <v>2245</v>
+      </c>
+      <c r="AF8" t="n">
         <v>2</v>
       </c>
-      <c r="AI8" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ8" t="s">
-        <v>2249</v>
+      <c r="AG8" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>2246</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>2222</v>
+        <v>2219</v>
       </c>
       <c r="B9" t="s">
         <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>2250</v>
+        <v>2247</v>
       </c>
       <c r="D9" t="s">
         <v>14</v>
@@ -8529,62 +8485,60 @@
         <v>23620</v>
       </c>
       <c r="U9" t="s">
-        <v>2251</v>
+        <v>2248</v>
       </c>
       <c r="V9" t="n">
         <v>225460</v>
       </c>
       <c r="W9" t="s">
-        <v>2225</v>
+        <v>2222</v>
       </c>
       <c r="X9" t="b">
         <v>1</v>
       </c>
-      <c r="Y9"/>
-      <c r="Z9"/>
-      <c r="AA9" t="s">
-        <v>2226</v>
-      </c>
-      <c r="AB9" t="n">
+      <c r="Y9" t="s">
+        <v>2223</v>
+      </c>
+      <c r="Z9" t="n">
         <v>-0.931569674529691</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AA9" t="n">
         <v>0.153599335928132</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>2249</v>
       </c>
       <c r="AD9" t="s">
         <v>18</v>
       </c>
       <c r="AE9" t="s">
-        <v>2252</v>
-      </c>
-      <c r="AF9" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG9" t="s">
-        <v>2252</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI9" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ9" t="s">
-        <v>2253</v>
+        <v>2249</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>2250</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>2222</v>
+        <v>2219</v>
       </c>
       <c r="B10" t="s">
         <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>2254</v>
+        <v>2251</v>
       </c>
       <c r="D10" t="s">
-        <v>2255</v>
+        <v>2252</v>
       </c>
       <c r="E10" t="n">
         <v>8208</v>
@@ -8635,62 +8589,60 @@
         <v>8208</v>
       </c>
       <c r="U10" t="s">
-        <v>2256</v>
+        <v>2253</v>
       </c>
       <c r="V10" t="n">
         <v>6426</v>
       </c>
       <c r="W10" t="s">
-        <v>2225</v>
+        <v>2222</v>
       </c>
       <c r="X10" t="b">
         <v>1</v>
       </c>
-      <c r="Y10"/>
-      <c r="Z10"/>
-      <c r="AA10" t="s">
-        <v>2226</v>
-      </c>
-      <c r="AB10" t="n">
+      <c r="Y10" t="s">
+        <v>2223</v>
+      </c>
+      <c r="Z10" t="n">
         <v>0.208348854299868</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AA10" t="n">
         <v>0.0499579905714109</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>2254</v>
       </c>
       <c r="AD10" t="s">
         <v>18</v>
       </c>
       <c r="AE10" t="s">
-        <v>2257</v>
-      </c>
-      <c r="AF10" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG10" t="s">
-        <v>2257</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="s">
-        <v>2258</v>
+        <v>2254</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>2255</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>2222</v>
+        <v>2219</v>
       </c>
       <c r="B11" t="s">
         <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>2259</v>
+        <v>2256</v>
       </c>
       <c r="D11" t="s">
-        <v>2260</v>
+        <v>2257</v>
       </c>
       <c r="E11" t="n">
         <v>32108</v>
@@ -8741,62 +8693,60 @@
         <v>43972</v>
       </c>
       <c r="U11" t="s">
-        <v>2247</v>
+        <v>2244</v>
       </c>
       <c r="V11" t="n">
         <v>1418430</v>
       </c>
       <c r="W11" t="s">
-        <v>2225</v>
+        <v>2222</v>
       </c>
       <c r="X11" t="b">
         <v>1</v>
       </c>
-      <c r="Y11"/>
-      <c r="Z11"/>
-      <c r="AA11" t="s">
-        <v>2226</v>
-      </c>
-      <c r="AB11" t="n">
+      <c r="Y11" t="s">
+        <v>2223</v>
+      </c>
+      <c r="Z11" t="n">
         <v>-0.342418042869689</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AA11" t="n">
         <v>0.0946692617699473</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>2245</v>
       </c>
       <c r="AD11" t="s">
         <v>18</v>
       </c>
       <c r="AE11" t="s">
-        <v>2248</v>
-      </c>
-      <c r="AF11" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG11" t="s">
-        <v>2248</v>
-      </c>
-      <c r="AH11" t="n">
+        <v>2245</v>
+      </c>
+      <c r="AF11" t="n">
         <v>3</v>
       </c>
-      <c r="AI11" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ11" t="s">
-        <v>2261</v>
+      <c r="AG11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>2258</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>2222</v>
+        <v>2219</v>
       </c>
       <c r="B12" t="s">
         <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>2262</v>
+        <v>2259</v>
       </c>
       <c r="D12" t="s">
-        <v>2263</v>
+        <v>2260</v>
       </c>
       <c r="E12" t="n">
         <v>16498</v>
@@ -8847,59 +8797,57 @@
         <v>39248</v>
       </c>
       <c r="U12" t="s">
-        <v>2264</v>
+        <v>2261</v>
       </c>
       <c r="V12" t="n">
         <v>1057455</v>
       </c>
       <c r="W12" t="s">
-        <v>2225</v>
+        <v>2222</v>
       </c>
       <c r="X12" t="b">
         <v>1</v>
       </c>
-      <c r="Y12"/>
-      <c r="Z12"/>
-      <c r="AA12" t="s">
-        <v>2226</v>
-      </c>
-      <c r="AB12" t="n">
+      <c r="Y12" t="s">
+        <v>2223</v>
+      </c>
+      <c r="Z12" t="n">
         <v>0.0550324061340405</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AA12" t="n">
         <v>0.0152442876765056</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>2262</v>
       </c>
       <c r="AD12" t="s">
         <v>18</v>
       </c>
       <c r="AE12" t="s">
-        <v>2265</v>
-      </c>
-      <c r="AF12" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG12" t="s">
-        <v>2265</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ12" t="s">
-        <v>2266</v>
+        <v>2262</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>2263</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>2222</v>
+        <v>2219</v>
       </c>
       <c r="B13" t="s">
         <v>15</v>
       </c>
       <c r="C13" t="s">
-        <v>2267</v>
+        <v>2264</v>
       </c>
       <c r="D13" t="s">
         <v>14</v>
@@ -8953,59 +8901,57 @@
         <v>23620</v>
       </c>
       <c r="U13" t="s">
-        <v>2247</v>
+        <v>2244</v>
       </c>
       <c r="V13" t="n">
         <v>1243230</v>
       </c>
       <c r="W13" t="s">
-        <v>2225</v>
+        <v>2222</v>
       </c>
       <c r="X13" t="b">
         <v>1</v>
       </c>
-      <c r="Y13"/>
-      <c r="Z13"/>
-      <c r="AA13" t="s">
-        <v>2226</v>
-      </c>
-      <c r="AB13" t="n">
+      <c r="Y13" t="s">
+        <v>2223</v>
+      </c>
+      <c r="Z13" t="n">
         <v>0.0669635952823567</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AA13" t="n">
         <v>0.0193446917159617</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>2245</v>
       </c>
       <c r="AD13" t="s">
         <v>18</v>
       </c>
       <c r="AE13" t="s">
-        <v>2248</v>
-      </c>
-      <c r="AF13" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG13" t="s">
-        <v>2248</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ13" t="s">
-        <v>2268</v>
+        <v>2245</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="s">
+        <v>2265</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>2222</v>
+        <v>2219</v>
       </c>
       <c r="B14" t="s">
         <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>2269</v>
+        <v>2266</v>
       </c>
       <c r="D14" t="s">
         <v>152</v>
@@ -9059,62 +9005,60 @@
         <v>32108</v>
       </c>
       <c r="U14" t="s">
-        <v>2251</v>
+        <v>2248</v>
       </c>
       <c r="V14" t="n">
         <v>71786</v>
       </c>
       <c r="W14" t="s">
-        <v>2225</v>
+        <v>2222</v>
       </c>
       <c r="X14" t="b">
         <v>1</v>
       </c>
-      <c r="Y14"/>
-      <c r="Z14"/>
-      <c r="AA14" t="s">
-        <v>2226</v>
-      </c>
-      <c r="AB14" t="n">
+      <c r="Y14" t="s">
+        <v>2223</v>
+      </c>
+      <c r="Z14" t="n">
         <v>-0.040560611573891</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AA14" t="n">
         <v>0.0120708943557139</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>2249</v>
       </c>
       <c r="AD14" t="s">
         <v>18</v>
       </c>
       <c r="AE14" t="s">
-        <v>2252</v>
-      </c>
-      <c r="AF14" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG14" t="s">
-        <v>2252</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="s">
-        <v>2270</v>
+        <v>2249</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="s">
+        <v>2267</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>2222</v>
+        <v>2219</v>
       </c>
       <c r="B15" t="s">
         <v>15</v>
       </c>
       <c r="C15" t="s">
-        <v>2271</v>
+        <v>2268</v>
       </c>
       <c r="D15" t="s">
-        <v>2272</v>
+        <v>2269</v>
       </c>
       <c r="E15" t="n">
         <v>42127</v>
@@ -9165,59 +9109,57 @@
         <v>45947</v>
       </c>
       <c r="U15" t="s">
-        <v>2224</v>
+        <v>2221</v>
       </c>
       <c r="V15" t="n">
         <v>295410</v>
       </c>
       <c r="W15" t="s">
-        <v>2225</v>
+        <v>2222</v>
       </c>
       <c r="X15" t="b">
         <v>1</v>
       </c>
-      <c r="Y15"/>
-      <c r="Z15"/>
-      <c r="AA15" t="s">
-        <v>2226</v>
-      </c>
-      <c r="AB15" t="n">
+      <c r="Y15" t="s">
+        <v>2223</v>
+      </c>
+      <c r="Z15" t="n">
         <v>0.134741877390322</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AA15" t="n">
         <v>0.0417765061356103</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>2224</v>
       </c>
       <c r="AD15" t="s">
         <v>18</v>
       </c>
       <c r="AE15" t="s">
-        <v>2227</v>
-      </c>
-      <c r="AF15" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG15" t="s">
-        <v>2227</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ15" t="s">
-        <v>2273</v>
+        <v>2224</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="s">
+        <v>2270</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>2222</v>
+        <v>2219</v>
       </c>
       <c r="B16" t="s">
         <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>2274</v>
+        <v>2271</v>
       </c>
       <c r="D16" t="s">
         <v>14</v>
@@ -9271,59 +9213,57 @@
         <v>23620</v>
       </c>
       <c r="U16" t="s">
-        <v>2224</v>
+        <v>2221</v>
       </c>
       <c r="V16" t="n">
         <v>270645</v>
       </c>
       <c r="W16" t="s">
-        <v>2225</v>
+        <v>2222</v>
       </c>
       <c r="X16" t="b">
         <v>1</v>
       </c>
-      <c r="Y16"/>
-      <c r="Z16"/>
-      <c r="AA16" t="s">
-        <v>2226</v>
-      </c>
-      <c r="AB16" t="n">
+      <c r="Y16" t="s">
+        <v>2223</v>
+      </c>
+      <c r="Z16" t="n">
         <v>-0.0761317359957112</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AA16" t="n">
         <v>0.0242032773500267</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>2224</v>
       </c>
       <c r="AD16" t="s">
         <v>18</v>
       </c>
       <c r="AE16" t="s">
-        <v>2227</v>
-      </c>
-      <c r="AF16" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG16" t="s">
-        <v>2227</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ16" t="s">
-        <v>2275</v>
+        <v>2224</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="s">
+        <v>2272</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>2222</v>
+        <v>2219</v>
       </c>
       <c r="B17" t="s">
         <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>2276</v>
+        <v>2273</v>
       </c>
       <c r="D17" t="s">
         <v>152</v>
@@ -9377,62 +9317,60 @@
         <v>32108</v>
       </c>
       <c r="U17" t="s">
-        <v>2241</v>
+        <v>2238</v>
       </c>
       <c r="V17" t="n">
         <v>429466</v>
       </c>
       <c r="W17" t="s">
-        <v>2225</v>
+        <v>2222</v>
       </c>
       <c r="X17" t="b">
         <v>1</v>
       </c>
-      <c r="Y17"/>
-      <c r="Z17"/>
-      <c r="AA17" t="s">
-        <v>2226</v>
-      </c>
-      <c r="AB17" t="n">
+      <c r="Y17" t="s">
+        <v>2223</v>
+      </c>
+      <c r="Z17" t="n">
         <v>-0.384765753582182</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AA17" t="n">
         <v>0.129774395392788</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>2239</v>
       </c>
       <c r="AD17" t="s">
         <v>18</v>
       </c>
       <c r="AE17" t="s">
-        <v>2242</v>
-      </c>
-      <c r="AF17" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG17" t="s">
-        <v>2242</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ17" t="s">
-        <v>2277</v>
+        <v>2239</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="s">
+        <v>2274</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>2222</v>
+        <v>2219</v>
       </c>
       <c r="B18" t="s">
         <v>15</v>
       </c>
       <c r="C18" t="s">
-        <v>2278</v>
+        <v>2275</v>
       </c>
       <c r="D18" t="s">
-        <v>2255</v>
+        <v>2252</v>
       </c>
       <c r="E18" t="n">
         <v>8208</v>
@@ -9483,62 +9421,60 @@
         <v>8208</v>
       </c>
       <c r="U18" t="s">
-        <v>2234</v>
+        <v>2231</v>
       </c>
       <c r="V18" t="n">
         <v>868477</v>
       </c>
       <c r="W18" t="s">
-        <v>2225</v>
+        <v>2222</v>
       </c>
       <c r="X18" t="b">
         <v>1</v>
       </c>
-      <c r="Y18"/>
-      <c r="Z18"/>
-      <c r="AA18" t="s">
-        <v>2226</v>
-      </c>
-      <c r="AB18" t="n">
+      <c r="Y18" t="s">
+        <v>2223</v>
+      </c>
+      <c r="Z18" t="n">
         <v>0.0767304882203801</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AA18" t="n">
         <v>0.0288653610679198</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>2232</v>
       </c>
       <c r="AD18" t="s">
         <v>18</v>
       </c>
       <c r="AE18" t="s">
-        <v>2235</v>
-      </c>
-      <c r="AF18" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG18" t="s">
-        <v>2235</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ18" t="s">
-        <v>2279</v>
+        <v>2232</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="s">
+        <v>2276</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>2222</v>
+        <v>2219</v>
       </c>
       <c r="B19" t="s">
         <v>15</v>
       </c>
       <c r="C19" t="s">
-        <v>2280</v>
+        <v>2277</v>
       </c>
       <c r="D19" t="s">
-        <v>2281</v>
+        <v>2278</v>
       </c>
       <c r="E19" t="n">
         <v>8208</v>
@@ -9589,62 +9525,60 @@
         <v>16498</v>
       </c>
       <c r="U19" t="s">
-        <v>2282</v>
+        <v>2279</v>
       </c>
       <c r="V19" t="n">
         <v>63810</v>
       </c>
       <c r="W19" t="s">
-        <v>2225</v>
+        <v>2222</v>
       </c>
       <c r="X19" t="b">
         <v>1</v>
       </c>
-      <c r="Y19"/>
-      <c r="Z19"/>
-      <c r="AA19" t="s">
-        <v>2226</v>
-      </c>
-      <c r="AB19" t="n">
+      <c r="Y19" t="s">
+        <v>2223</v>
+      </c>
+      <c r="Z19" t="n">
         <v>0.155276038287615</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AA19" t="n">
         <v>0.0631997353269653</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>2280</v>
       </c>
       <c r="AD19" t="s">
         <v>18</v>
       </c>
       <c r="AE19" t="s">
-        <v>2283</v>
-      </c>
-      <c r="AF19" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG19" t="s">
-        <v>2283</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ19" t="s">
-        <v>2284</v>
+        <v>2280</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="s">
+        <v>2281</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>2222</v>
+        <v>2219</v>
       </c>
       <c r="B20" t="s">
         <v>15</v>
       </c>
       <c r="C20" t="s">
-        <v>2285</v>
+        <v>2282</v>
       </c>
       <c r="D20" t="s">
-        <v>2281</v>
+        <v>2278</v>
       </c>
       <c r="E20" t="n">
         <v>8208</v>
@@ -9695,59 +9629,57 @@
         <v>16498</v>
       </c>
       <c r="U20" t="s">
-        <v>2247</v>
+        <v>2244</v>
       </c>
       <c r="V20" t="n">
         <v>1443630</v>
       </c>
       <c r="W20" t="s">
-        <v>2225</v>
+        <v>2222</v>
       </c>
       <c r="X20" t="b">
         <v>1</v>
       </c>
-      <c r="Y20"/>
-      <c r="Z20"/>
-      <c r="AA20" t="s">
-        <v>2226</v>
-      </c>
-      <c r="AB20" t="n">
+      <c r="Y20" t="s">
+        <v>2223</v>
+      </c>
+      <c r="Z20" t="n">
         <v>0.0640186662095973</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AA20" t="n">
         <v>0.0300262364642089</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>2245</v>
       </c>
       <c r="AD20" t="s">
         <v>18</v>
       </c>
       <c r="AE20" t="s">
-        <v>2248</v>
-      </c>
-      <c r="AF20" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG20" t="s">
-        <v>2248</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ20" t="s">
-        <v>2286</v>
+        <v>2245</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="s">
+        <v>2283</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>2222</v>
+        <v>2219</v>
       </c>
       <c r="B21" t="s">
         <v>15</v>
       </c>
       <c r="C21" t="s">
-        <v>2287</v>
+        <v>2284</v>
       </c>
       <c r="D21" t="s">
         <v>152</v>
@@ -9801,62 +9733,60 @@
         <v>32108</v>
       </c>
       <c r="U21" t="s">
-        <v>2288</v>
+        <v>2285</v>
       </c>
       <c r="V21" t="n">
         <v>900150</v>
       </c>
       <c r="W21" t="s">
-        <v>2225</v>
+        <v>2222</v>
       </c>
       <c r="X21" t="b">
         <v>1</v>
       </c>
-      <c r="Y21"/>
-      <c r="Z21"/>
-      <c r="AA21" t="s">
-        <v>2226</v>
-      </c>
-      <c r="AB21" t="n">
+      <c r="Y21" t="s">
+        <v>2223</v>
+      </c>
+      <c r="Z21" t="n">
         <v>-0.0319285288582089</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="AA21" t="n">
         <v>0.0127734213090584</v>
+      </c>
+      <c r="AB21" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>2286</v>
       </c>
       <c r="AD21" t="s">
         <v>18</v>
       </c>
       <c r="AE21" t="s">
-        <v>2289</v>
-      </c>
-      <c r="AF21" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG21" t="s">
-        <v>2289</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ21" t="s">
-        <v>2290</v>
+        <v>2286</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="s">
+        <v>2287</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>2222</v>
+        <v>2219</v>
       </c>
       <c r="B22" t="s">
         <v>15</v>
       </c>
       <c r="C22" t="s">
-        <v>2291</v>
+        <v>2288</v>
       </c>
       <c r="D22" t="s">
-        <v>2281</v>
+        <v>2278</v>
       </c>
       <c r="E22" t="n">
         <v>8208</v>
@@ -9907,62 +9837,60 @@
         <v>16498</v>
       </c>
       <c r="U22" t="s">
-        <v>2282</v>
+        <v>2279</v>
       </c>
       <c r="V22" t="n">
         <v>8971</v>
       </c>
       <c r="W22" t="s">
-        <v>2225</v>
+        <v>2222</v>
       </c>
       <c r="X22" t="b">
         <v>1</v>
       </c>
-      <c r="Y22"/>
-      <c r="Z22"/>
-      <c r="AA22" t="s">
-        <v>2226</v>
-      </c>
-      <c r="AB22" t="n">
+      <c r="Y22" t="s">
+        <v>2223</v>
+      </c>
+      <c r="Z22" t="n">
         <v>0.0988695672358149</v>
       </c>
-      <c r="AC22" t="n">
+      <c r="AA22" t="n">
         <v>0.0477013343026073</v>
+      </c>
+      <c r="AB22" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC22" t="s">
+        <v>2280</v>
       </c>
       <c r="AD22" t="s">
         <v>18</v>
       </c>
       <c r="AE22" t="s">
-        <v>2283</v>
-      </c>
-      <c r="AF22" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG22" t="s">
-        <v>2283</v>
-      </c>
-      <c r="AH22" t="n">
+        <v>2280</v>
+      </c>
+      <c r="AF22" t="n">
         <v>2</v>
       </c>
-      <c r="AI22" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ22" t="s">
-        <v>2292</v>
+      <c r="AG22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH22" t="s">
+        <v>2289</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>2222</v>
+        <v>2219</v>
       </c>
       <c r="B23" t="s">
         <v>15</v>
       </c>
       <c r="C23" t="s">
-        <v>2293</v>
+        <v>2290</v>
       </c>
       <c r="D23" t="s">
-        <v>2255</v>
+        <v>2252</v>
       </c>
       <c r="E23" t="n">
         <v>8208</v>
@@ -10013,59 +9941,57 @@
         <v>8208</v>
       </c>
       <c r="U23" t="s">
-        <v>2241</v>
+        <v>2238</v>
       </c>
       <c r="V23" t="n">
         <v>37053</v>
       </c>
       <c r="W23" t="s">
-        <v>2225</v>
+        <v>2222</v>
       </c>
       <c r="X23" t="b">
         <v>1</v>
       </c>
-      <c r="Y23"/>
-      <c r="Z23"/>
-      <c r="AA23" t="s">
-        <v>2226</v>
-      </c>
-      <c r="AB23" t="n">
+      <c r="Y23" t="s">
+        <v>2223</v>
+      </c>
+      <c r="Z23" t="n">
         <v>0.0689656605616588</v>
       </c>
-      <c r="AC23" t="n">
+      <c r="AA23" t="n">
         <v>0.0387285610705909</v>
+      </c>
+      <c r="AB23" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC23" t="s">
+        <v>2239</v>
       </c>
       <c r="AD23" t="s">
         <v>18</v>
       </c>
       <c r="AE23" t="s">
-        <v>2242</v>
-      </c>
-      <c r="AF23" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG23" t="s">
-        <v>2242</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI23" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ23" t="s">
-        <v>2294</v>
+        <v>2239</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH23" t="s">
+        <v>2291</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>2222</v>
+        <v>2219</v>
       </c>
       <c r="B24" t="s">
         <v>15</v>
       </c>
       <c r="C24" t="s">
-        <v>2295</v>
+        <v>2292</v>
       </c>
       <c r="D24" t="s">
         <v>152</v>
@@ -10119,59 +10045,57 @@
         <v>32108</v>
       </c>
       <c r="U24" t="s">
-        <v>2241</v>
+        <v>2238</v>
       </c>
       <c r="V24" t="n">
         <v>477671</v>
       </c>
       <c r="W24" t="s">
-        <v>2225</v>
+        <v>2222</v>
       </c>
       <c r="X24" t="b">
         <v>1</v>
       </c>
-      <c r="Y24"/>
-      <c r="Z24"/>
-      <c r="AA24" t="s">
-        <v>2226</v>
-      </c>
-      <c r="AB24" t="n">
+      <c r="Y24" t="s">
+        <v>2223</v>
+      </c>
+      <c r="Z24" t="n">
         <v>0.0140067180310389</v>
       </c>
-      <c r="AC24" t="n">
+      <c r="AA24" t="n">
         <v>0.00707423557152582</v>
+      </c>
+      <c r="AB24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC24" t="s">
+        <v>2239</v>
       </c>
       <c r="AD24" t="s">
         <v>18</v>
       </c>
       <c r="AE24" t="s">
-        <v>2242</v>
-      </c>
-      <c r="AF24" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG24" t="s">
-        <v>2242</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI24" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ24" t="s">
-        <v>2296</v>
+        <v>2239</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH24" t="s">
+        <v>2293</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>2222</v>
+        <v>2219</v>
       </c>
       <c r="B25" t="s">
         <v>15</v>
       </c>
       <c r="C25" t="s">
-        <v>2297</v>
+        <v>2294</v>
       </c>
       <c r="D25" t="s">
         <v>14</v>
@@ -10225,27 +10149,31 @@
         <v>23620</v>
       </c>
       <c r="U25" t="s">
-        <v>2238</v>
+        <v>2235</v>
       </c>
       <c r="V25" t="n">
         <v>153293</v>
       </c>
       <c r="W25" t="s">
-        <v>2225</v>
+        <v>2222</v>
       </c>
       <c r="X25" t="b">
         <v>1</v>
       </c>
-      <c r="Y25"/>
-      <c r="Z25"/>
-      <c r="AA25" t="s">
-        <v>2226</v>
-      </c>
-      <c r="AB25" t="n">
+      <c r="Y25" t="s">
+        <v>2223</v>
+      </c>
+      <c r="Z25" t="n">
         <v>0.0325482288473463</v>
       </c>
-      <c r="AC25" t="n">
+      <c r="AA25" t="n">
         <v>0.0214199013605089</v>
+      </c>
+      <c r="AB25" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC25" t="s">
+        <v>38</v>
       </c>
       <c r="AD25" t="s">
         <v>18</v>
@@ -10253,31 +10181,25 @@
       <c r="AE25" t="s">
         <v>38</v>
       </c>
-      <c r="AF25" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG25" t="s">
-        <v>38</v>
-      </c>
-      <c r="AH25" t="n">
+      <c r="AF25" t="n">
         <v>3</v>
       </c>
-      <c r="AI25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ25" t="s">
-        <v>2298</v>
+      <c r="AG25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH25" t="s">
+        <v>2295</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>2222</v>
+        <v>2219</v>
       </c>
       <c r="B26" t="s">
         <v>15</v>
       </c>
       <c r="C26" t="s">
-        <v>2299</v>
+        <v>2296</v>
       </c>
       <c r="D26" t="s">
         <v>14</v>
@@ -10331,59 +10253,57 @@
         <v>23620</v>
       </c>
       <c r="U26" t="s">
-        <v>2300</v>
+        <v>2297</v>
       </c>
       <c r="V26" t="n">
         <v>636780</v>
       </c>
       <c r="W26" t="s">
-        <v>2225</v>
+        <v>2222</v>
       </c>
       <c r="X26" t="b">
         <v>1</v>
       </c>
-      <c r="Y26"/>
-      <c r="Z26"/>
-      <c r="AA26" t="s">
-        <v>2226</v>
-      </c>
-      <c r="AB26" t="n">
+      <c r="Y26" t="s">
+        <v>2223</v>
+      </c>
+      <c r="Z26" t="n">
         <v>0.0426507916804654</v>
       </c>
-      <c r="AC26" t="n">
+      <c r="AA26" t="n">
         <v>0.0184770454453693</v>
+      </c>
+      <c r="AB26" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC26" t="s">
+        <v>2298</v>
       </c>
       <c r="AD26" t="s">
         <v>18</v>
       </c>
       <c r="AE26" t="s">
-        <v>2301</v>
-      </c>
-      <c r="AF26" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG26" t="s">
-        <v>2301</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ26" t="s">
-        <v>2302</v>
+        <v>2298</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="s">
+        <v>2299</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>2222</v>
+        <v>2219</v>
       </c>
       <c r="B27" t="s">
         <v>15</v>
       </c>
       <c r="C27" t="s">
-        <v>2303</v>
+        <v>2300</v>
       </c>
       <c r="D27" t="s">
         <v>152</v>
@@ -10437,48 +10357,46 @@
         <v>32108</v>
       </c>
       <c r="U27" t="s">
-        <v>2224</v>
+        <v>2221</v>
       </c>
       <c r="V27" t="n">
         <v>159580</v>
       </c>
       <c r="W27" t="s">
-        <v>2225</v>
+        <v>2222</v>
       </c>
       <c r="X27" t="b">
         <v>1</v>
       </c>
-      <c r="Y27"/>
-      <c r="Z27"/>
-      <c r="AA27" t="s">
-        <v>2226</v>
-      </c>
-      <c r="AB27" t="n">
+      <c r="Y27" t="s">
+        <v>2223</v>
+      </c>
+      <c r="Z27" t="n">
         <v>0.0630603968207397</v>
       </c>
-      <c r="AC27" t="n">
+      <c r="AA27" t="n">
         <v>0.0317382172482277</v>
+      </c>
+      <c r="AB27" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC27" t="s">
+        <v>2224</v>
       </c>
       <c r="AD27" t="s">
         <v>18</v>
       </c>
       <c r="AE27" t="s">
-        <v>2227</v>
-      </c>
-      <c r="AF27" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG27" t="s">
-        <v>2227</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ27" t="s">
-        <v>2304</v>
+        <v>2224</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="s">
+        <v>2301</v>
       </c>
     </row>
   </sheetData>
@@ -10557,37 +10475,28 @@
         <v>2208</v>
       </c>
       <c r="V1" t="s">
-        <v>2305</v>
+        <v>122</v>
       </c>
       <c r="W1" t="s">
-        <v>2306</v>
+        <v>2212</v>
       </c>
       <c r="X1" t="s">
-        <v>2307</v>
+        <v>2213</v>
       </c>
       <c r="Y1" t="s">
-        <v>2308</v>
+        <v>2214</v>
       </c>
       <c r="Z1" t="s">
-        <v>2309</v>
+        <v>12</v>
       </c>
       <c r="AA1" t="s">
-        <v>2216</v>
+        <v>2215</v>
       </c>
       <c r="AB1" t="s">
-        <v>2217</v>
+        <v>2302</v>
       </c>
       <c r="AC1" t="s">
-        <v>12</v>
-      </c>
-      <c r="AD1" t="s">
         <v>2218</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>2310</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>2221</v>
       </c>
     </row>
     <row r="2">
@@ -10655,36 +10564,27 @@
         <v>23923</v>
       </c>
       <c r="V2" t="n">
-        <v>-35.2010222848177</v>
+        <v>-1.60761592687895</v>
       </c>
       <c r="W2" t="n">
-        <v>-28.5685967441221</v>
-      </c>
-      <c r="X2" t="n">
-        <v>-24.5852667523832</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-20.3117471855015</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-22.2860718780244</v>
+        <v>0.059534912354601</v>
+      </c>
+      <c r="X2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>18</v>
       </c>
       <c r="AA2" t="s">
         <v>18</v>
       </c>
-      <c r="AB2" t="s">
-        <v>18</v>
+      <c r="AB2" t="n">
+        <v>0</v>
       </c>
       <c r="AC2" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="s">
         <v>93</v>
       </c>
     </row>
@@ -10693,10 +10593,10 @@
         <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>2311</v>
+        <v>2303</v>
       </c>
       <c r="C3" t="s">
-        <v>2255</v>
+        <v>2252</v>
       </c>
       <c r="D3" t="n">
         <v>8208</v>
@@ -10753,37 +10653,28 @@
         <v>7244</v>
       </c>
       <c r="V3" t="n">
-        <v>-9.9662355031393</v>
+        <v>-0.891661370779768</v>
       </c>
       <c r="W3" t="n">
-        <v>-6.9758919575292</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-7.65115943591409</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>-7.10014279116754</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>-5.85632293656809</v>
+        <v>0.115807422455049</v>
+      </c>
+      <c r="X3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>18</v>
       </c>
       <c r="AA3" t="s">
         <v>18</v>
       </c>
-      <c r="AB3" t="s">
-        <v>18</v>
+      <c r="AB3" t="n">
+        <v>0</v>
       </c>
       <c r="AC3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>2312</v>
+        <v>2304</v>
       </c>
     </row>
     <row r="4">
@@ -10791,10 +10682,10 @@
         <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>2313</v>
+        <v>2305</v>
       </c>
       <c r="C4" t="s">
-        <v>2281</v>
+        <v>2278</v>
       </c>
       <c r="D4" t="n">
         <v>8208</v>
@@ -10851,37 +10742,28 @@
         <v>17064</v>
       </c>
       <c r="V4" t="n">
-        <v>2.94885130635809</v>
+        <v>0.32018154251846</v>
       </c>
       <c r="W4" t="n">
-        <v>3.13170271047533</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.12994755428586</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>3.17756939572797</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3.43097332476299</v>
+        <v>0.107597588252934</v>
+      </c>
+      <c r="X4" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>18</v>
       </c>
       <c r="AA4" t="s">
         <v>18</v>
       </c>
-      <c r="AB4" t="s">
-        <v>18</v>
+      <c r="AB4" t="n">
+        <v>0</v>
       </c>
       <c r="AC4" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>2314</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="5">
@@ -10889,7 +10771,7 @@
         <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>2315</v>
+        <v>2307</v>
       </c>
       <c r="C5" t="s">
         <v>14</v>
@@ -10949,37 +10831,28 @@
         <v>18940</v>
       </c>
       <c r="V5" t="n">
-        <v>1.71784422015146</v>
+        <v>0.120581756179321</v>
       </c>
       <c r="W5" t="n">
-        <v>3.55421029911446</v>
-      </c>
-      <c r="X5" t="n">
-        <v>3.68024494753991</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>3.15271405464275</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0.268112922584203</v>
+        <v>0.0498487989425352</v>
+      </c>
+      <c r="X5" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>18</v>
       </c>
       <c r="AA5" t="s">
         <v>18</v>
       </c>
-      <c r="AB5" t="s">
-        <v>18</v>
+      <c r="AB5" t="n">
+        <v>0</v>
       </c>
       <c r="AC5" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>2316</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="6">
@@ -10987,10 +10860,10 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>2317</v>
+        <v>2309</v>
       </c>
       <c r="C6" t="s">
-        <v>2318</v>
+        <v>2310</v>
       </c>
       <c r="D6" t="n">
         <v>70163</v>
@@ -11047,37 +10920,28 @@
         <v>25918</v>
       </c>
       <c r="V6" t="n">
-        <v>0.712221080163524</v>
+        <v>-0.404025444470436</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.229420516764895</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-2.82916162649998</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>-0.595418621435909</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>-3.29694254134861</v>
+        <v>0.40756228538614</v>
+      </c>
+      <c r="X6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>18</v>
       </c>
       <c r="AA6" t="s">
         <v>18</v>
       </c>
-      <c r="AB6" t="s">
-        <v>18</v>
+      <c r="AB6" t="n">
+        <v>0.00065359477124183</v>
       </c>
       <c r="AC6" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0.00065359477124183</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>2317</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="7">
@@ -11085,10 +10949,10 @@
         <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>2319</v>
+        <v>2311</v>
       </c>
       <c r="C7" t="s">
-        <v>2320</v>
+        <v>2312</v>
       </c>
       <c r="D7" t="n">
         <v>81991</v>
@@ -11145,37 +11009,28 @@
         <v>10198</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.88229807254263</v>
+        <v>-0.11749016744584</v>
       </c>
       <c r="W7" t="n">
-        <v>0.00769713300856457</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-0.226950279866554</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>-0.332703250921967</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>-3.41723697073741</v>
+        <v>0.0982260641328271</v>
+      </c>
+      <c r="X7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>18</v>
       </c>
       <c r="AA7" t="s">
         <v>18</v>
       </c>
-      <c r="AB7" t="s">
-        <v>18</v>
+      <c r="AB7" t="n">
+        <v>0.0367959921605441</v>
       </c>
       <c r="AC7" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0.0367959921605441</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>2319</v>
+        <v>2311</v>
       </c>
     </row>
   </sheetData>
@@ -11206,34 +11061,34 @@
         <v>27</v>
       </c>
       <c r="F1" t="s">
-        <v>2321</v>
+        <v>2313</v>
       </c>
       <c r="G1" t="s">
         <v>668</v>
       </c>
       <c r="H1" t="s">
-        <v>2322</v>
+        <v>2314</v>
       </c>
       <c r="I1" t="s">
-        <v>2323</v>
+        <v>2315</v>
       </c>
       <c r="J1" t="s">
         <v>674</v>
       </c>
       <c r="K1" t="s">
-        <v>2324</v>
+        <v>2316</v>
       </c>
       <c r="L1" t="s">
-        <v>2325</v>
+        <v>2317</v>
       </c>
       <c r="M1" t="s">
-        <v>2326</v>
+        <v>2318</v>
       </c>
       <c r="N1" t="s">
-        <v>2327</v>
+        <v>2319</v>
       </c>
       <c r="O1" t="s">
-        <v>2328</v>
+        <v>2320</v>
       </c>
       <c r="P1" t="s">
         <v>2208</v>
@@ -11253,30 +11108,30 @@
         <v>4224</v>
       </c>
       <c r="E2" t="s">
-        <v>2329</v>
+        <v>2321</v>
       </c>
       <c r="F2" t="s">
-        <v>2330</v>
+        <v>2322</v>
       </c>
       <c r="G2" t="s">
-        <v>2328</v>
+        <v>2320</v>
       </c>
       <c r="H2"/>
       <c r="I2"/>
       <c r="J2" t="s">
-        <v>2331</v>
+        <v>2323</v>
       </c>
       <c r="K2" t="s">
-        <v>2332</v>
+        <v>2324</v>
       </c>
       <c r="L2" t="s">
-        <v>2331</v>
+        <v>2323</v>
       </c>
       <c r="M2" t="s">
-        <v>2333</v>
+        <v>2325</v>
       </c>
       <c r="N2" t="s">
-        <v>2334</v>
+        <v>2326</v>
       </c>
       <c r="O2"/>
       <c r="P2" t="n">
@@ -11297,33 +11152,33 @@
         <v>1140</v>
       </c>
       <c r="E3" t="s">
-        <v>2335</v>
+        <v>2327</v>
       </c>
       <c r="F3" t="s">
-        <v>2330</v>
+        <v>2322</v>
       </c>
       <c r="G3" t="s">
-        <v>2328</v>
+        <v>2320</v>
       </c>
       <c r="H3"/>
       <c r="I3"/>
       <c r="J3" t="s">
-        <v>2311</v>
+        <v>2303</v>
       </c>
       <c r="K3" t="s">
-        <v>2336</v>
+        <v>2328</v>
       </c>
       <c r="L3" t="s">
-        <v>2311</v>
+        <v>2303</v>
       </c>
       <c r="M3" t="s">
-        <v>2337</v>
+        <v>2329</v>
       </c>
       <c r="N3" t="s">
-        <v>2338</v>
+        <v>2330</v>
       </c>
       <c r="O3" t="s">
-        <v>2312</v>
+        <v>2304</v>
       </c>
       <c r="P3" t="n">
         <v>7814</v>
@@ -11343,30 +11198,30 @@
         <v>1098</v>
       </c>
       <c r="E4" t="s">
-        <v>2335</v>
+        <v>2327</v>
       </c>
       <c r="F4" t="s">
-        <v>2330</v>
+        <v>2322</v>
       </c>
       <c r="G4" t="s">
-        <v>2328</v>
+        <v>2320</v>
       </c>
       <c r="H4"/>
       <c r="I4"/>
       <c r="J4" t="s">
-        <v>2319</v>
+        <v>2311</v>
       </c>
       <c r="K4" t="s">
-        <v>2339</v>
+        <v>2331</v>
       </c>
       <c r="L4" t="s">
-        <v>2319</v>
+        <v>2311</v>
       </c>
       <c r="M4" t="s">
-        <v>2340</v>
+        <v>2332</v>
       </c>
       <c r="N4" t="s">
-        <v>2338</v>
+        <v>2330</v>
       </c>
       <c r="O4"/>
       <c r="P4" t="n">
@@ -11387,33 +11242,33 @@
         <v>1692</v>
       </c>
       <c r="E5" t="s">
-        <v>2329</v>
+        <v>2321</v>
       </c>
       <c r="F5" t="s">
-        <v>2330</v>
+        <v>2322</v>
       </c>
       <c r="G5" t="s">
-        <v>2328</v>
+        <v>2320</v>
       </c>
       <c r="H5"/>
       <c r="I5"/>
       <c r="J5" t="s">
-        <v>2341</v>
+        <v>2333</v>
       </c>
       <c r="K5" t="s">
-        <v>2342</v>
+        <v>2334</v>
       </c>
       <c r="L5" t="s">
-        <v>2341</v>
+        <v>2333</v>
       </c>
       <c r="M5" t="s">
-        <v>2343</v>
+        <v>2335</v>
       </c>
       <c r="N5" t="s">
-        <v>2338</v>
+        <v>2330</v>
       </c>
       <c r="O5" t="s">
-        <v>2344</v>
+        <v>2336</v>
       </c>
       <c r="P5" t="n">
         <v>12328</v>
@@ -11433,33 +11288,33 @@
         <v>213</v>
       </c>
       <c r="E6" t="s">
-        <v>2329</v>
+        <v>2321</v>
       </c>
       <c r="F6" t="s">
-        <v>2330</v>
+        <v>2322</v>
       </c>
       <c r="G6" t="s">
-        <v>2328</v>
+        <v>2320</v>
       </c>
       <c r="H6"/>
       <c r="I6"/>
       <c r="J6" t="s">
-        <v>2345</v>
+        <v>2337</v>
       </c>
       <c r="K6" t="s">
-        <v>2346</v>
+        <v>2338</v>
       </c>
       <c r="L6" t="s">
-        <v>2345</v>
+        <v>2337</v>
       </c>
       <c r="M6" t="s">
-        <v>2347</v>
+        <v>2339</v>
       </c>
       <c r="N6" t="s">
-        <v>2338</v>
+        <v>2330</v>
       </c>
       <c r="O6" t="s">
-        <v>2348</v>
+        <v>2340</v>
       </c>
       <c r="P6" t="n">
         <v>14647</v>
@@ -11479,33 +11334,33 @@
         <v>1542</v>
       </c>
       <c r="E7" t="s">
-        <v>2329</v>
+        <v>2321</v>
       </c>
       <c r="F7" t="s">
-        <v>2330</v>
+        <v>2322</v>
       </c>
       <c r="G7" t="s">
-        <v>2328</v>
+        <v>2320</v>
       </c>
       <c r="H7"/>
       <c r="I7"/>
       <c r="J7" t="s">
-        <v>2349</v>
+        <v>2341</v>
       </c>
       <c r="K7" t="s">
-        <v>2350</v>
+        <v>2342</v>
       </c>
       <c r="L7" t="s">
-        <v>2349</v>
+        <v>2341</v>
       </c>
       <c r="M7" t="s">
-        <v>2340</v>
+        <v>2332</v>
       </c>
       <c r="N7" t="s">
-        <v>2338</v>
+        <v>2330</v>
       </c>
       <c r="O7" t="s">
-        <v>2351</v>
+        <v>2343</v>
       </c>
       <c r="P7" t="n">
         <v>15906</v>
@@ -11525,33 +11380,33 @@
         <v>1746</v>
       </c>
       <c r="E8" t="s">
-        <v>2335</v>
+        <v>2327</v>
       </c>
       <c r="F8" t="s">
-        <v>2330</v>
+        <v>2322</v>
       </c>
       <c r="G8" t="s">
-        <v>2328</v>
+        <v>2320</v>
       </c>
       <c r="H8"/>
       <c r="I8"/>
       <c r="J8" t="s">
-        <v>2313</v>
+        <v>2305</v>
       </c>
       <c r="K8" t="s">
-        <v>2352</v>
+        <v>2344</v>
       </c>
       <c r="L8" t="s">
-        <v>2313</v>
+        <v>2305</v>
       </c>
       <c r="M8" t="s">
-        <v>2353</v>
+        <v>2345</v>
       </c>
       <c r="N8" t="s">
-        <v>2338</v>
+        <v>2330</v>
       </c>
       <c r="O8" t="s">
-        <v>2314</v>
+        <v>2306</v>
       </c>
       <c r="P8" t="n">
         <v>17936</v>
@@ -11571,33 +11426,33 @@
         <v>1476</v>
       </c>
       <c r="E9" t="s">
-        <v>2329</v>
+        <v>2321</v>
       </c>
       <c r="F9" t="s">
-        <v>2330</v>
+        <v>2322</v>
       </c>
       <c r="G9" t="s">
-        <v>2328</v>
+        <v>2320</v>
       </c>
       <c r="H9"/>
       <c r="I9"/>
       <c r="J9" t="s">
-        <v>2315</v>
+        <v>2307</v>
       </c>
       <c r="K9" t="s">
-        <v>2354</v>
+        <v>2346</v>
       </c>
       <c r="L9" t="s">
-        <v>2315</v>
+        <v>2307</v>
       </c>
       <c r="M9" t="s">
-        <v>2355</v>
+        <v>2347</v>
       </c>
       <c r="N9" t="s">
-        <v>2338</v>
+        <v>2330</v>
       </c>
       <c r="O9" t="s">
-        <v>2316</v>
+        <v>2308</v>
       </c>
       <c r="P9" t="n">
         <v>19798</v>
@@ -11617,33 +11472,33 @@
         <v>939</v>
       </c>
       <c r="E10" t="s">
-        <v>2329</v>
+        <v>2321</v>
       </c>
       <c r="F10" t="s">
-        <v>2330</v>
+        <v>2322</v>
       </c>
       <c r="G10" t="s">
-        <v>2328</v>
+        <v>2320</v>
       </c>
       <c r="H10"/>
       <c r="I10"/>
       <c r="J10" t="s">
-        <v>2356</v>
+        <v>2348</v>
       </c>
       <c r="K10" t="s">
-        <v>2357</v>
+        <v>2349</v>
       </c>
       <c r="L10" t="s">
-        <v>2356</v>
+        <v>2348</v>
       </c>
       <c r="M10" t="s">
-        <v>2358</v>
+        <v>2350</v>
       </c>
       <c r="N10" t="s">
-        <v>2338</v>
+        <v>2330</v>
       </c>
       <c r="O10" t="s">
-        <v>2359</v>
+        <v>2351</v>
       </c>
       <c r="P10" t="n">
         <v>21230</v>
@@ -11663,33 +11518,33 @@
         <v>1636</v>
       </c>
       <c r="E11" t="s">
-        <v>2329</v>
+        <v>2321</v>
       </c>
       <c r="F11" t="s">
-        <v>2330</v>
+        <v>2322</v>
       </c>
       <c r="G11" t="s">
-        <v>2328</v>
+        <v>2320</v>
       </c>
       <c r="H11"/>
       <c r="I11"/>
       <c r="J11" t="s">
-        <v>2360</v>
+        <v>2352</v>
       </c>
       <c r="K11" t="s">
-        <v>2361</v>
+        <v>2353</v>
       </c>
       <c r="L11" t="s">
-        <v>2360</v>
+        <v>2352</v>
       </c>
       <c r="M11" t="s">
-        <v>2362</v>
+        <v>2354</v>
       </c>
       <c r="N11" t="s">
-        <v>2338</v>
+        <v>2330</v>
       </c>
       <c r="O11" t="s">
-        <v>2363</v>
+        <v>2355</v>
       </c>
       <c r="P11" t="n">
         <v>22866</v>
@@ -11709,13 +11564,13 @@
         <v>1764</v>
       </c>
       <c r="E12" t="s">
-        <v>2329</v>
+        <v>2321</v>
       </c>
       <c r="F12" t="s">
-        <v>2330</v>
+        <v>2322</v>
       </c>
       <c r="G12" t="s">
-        <v>2328</v>
+        <v>2320</v>
       </c>
       <c r="H12"/>
       <c r="I12"/>
@@ -11723,16 +11578,16 @@
         <v>92</v>
       </c>
       <c r="K12" t="s">
-        <v>2364</v>
+        <v>2356</v>
       </c>
       <c r="L12" t="s">
         <v>92</v>
       </c>
       <c r="M12" t="s">
-        <v>2365</v>
+        <v>2357</v>
       </c>
       <c r="N12" t="s">
-        <v>2338</v>
+        <v>2330</v>
       </c>
       <c r="O12" t="s">
         <v>93</v>
@@ -11755,30 +11610,30 @@
         <v>381</v>
       </c>
       <c r="E13" t="s">
-        <v>2329</v>
+        <v>2321</v>
       </c>
       <c r="F13" t="s">
-        <v>2330</v>
+        <v>2322</v>
       </c>
       <c r="G13" t="s">
-        <v>2328</v>
+        <v>2320</v>
       </c>
       <c r="H13"/>
       <c r="I13"/>
       <c r="J13" t="s">
-        <v>2317</v>
+        <v>2309</v>
       </c>
       <c r="K13" t="s">
-        <v>2366</v>
+        <v>2358</v>
       </c>
       <c r="L13" t="s">
-        <v>2317</v>
+        <v>2309</v>
       </c>
       <c r="M13" t="s">
-        <v>2367</v>
+        <v>2359</v>
       </c>
       <c r="N13" t="s">
-        <v>2334</v>
+        <v>2326</v>
       </c>
       <c r="O13"/>
       <c r="P13" t="n">
@@ -11799,33 +11654,33 @@
         <v>933</v>
       </c>
       <c r="E14" t="s">
-        <v>2335</v>
+        <v>2327</v>
       </c>
       <c r="F14" t="s">
-        <v>2330</v>
+        <v>2322</v>
       </c>
       <c r="G14" t="s">
-        <v>2328</v>
+        <v>2320</v>
       </c>
       <c r="H14"/>
       <c r="I14"/>
       <c r="J14" t="s">
-        <v>2368</v>
+        <v>2360</v>
       </c>
       <c r="K14" t="s">
-        <v>2369</v>
+        <v>2361</v>
       </c>
       <c r="L14" t="s">
-        <v>2368</v>
+        <v>2360</v>
       </c>
       <c r="M14" t="s">
-        <v>2370</v>
+        <v>2362</v>
       </c>
       <c r="N14" t="s">
-        <v>2338</v>
+        <v>2330</v>
       </c>
       <c r="O14" t="s">
-        <v>2371</v>
+        <v>2363</v>
       </c>
       <c r="P14" t="n">
         <v>27396</v>
@@ -11845,33 +11700,33 @@
         <v>1542</v>
       </c>
       <c r="E15" t="s">
-        <v>2329</v>
+        <v>2321</v>
       </c>
       <c r="F15" t="s">
-        <v>2330</v>
+        <v>2322</v>
       </c>
       <c r="G15" t="s">
-        <v>2328</v>
+        <v>2320</v>
       </c>
       <c r="H15"/>
       <c r="I15"/>
       <c r="J15" t="s">
-        <v>2372</v>
+        <v>2364</v>
       </c>
       <c r="K15" t="s">
-        <v>2373</v>
+        <v>2365</v>
       </c>
       <c r="L15" t="s">
-        <v>2372</v>
+        <v>2364</v>
       </c>
       <c r="M15" t="s">
-        <v>2374</v>
+        <v>2366</v>
       </c>
       <c r="N15" t="s">
-        <v>2338</v>
+        <v>2330</v>
       </c>
       <c r="O15" t="s">
-        <v>2375</v>
+        <v>2367</v>
       </c>
       <c r="P15" t="n">
         <v>29036</v>
@@ -11891,30 +11746,30 @@
         <v>1074</v>
       </c>
       <c r="E16" t="s">
-        <v>2335</v>
+        <v>2327</v>
       </c>
       <c r="F16" t="s">
-        <v>2330</v>
+        <v>2322</v>
       </c>
       <c r="G16" t="s">
-        <v>2328</v>
+        <v>2320</v>
       </c>
       <c r="H16"/>
       <c r="I16"/>
       <c r="J16" t="s">
-        <v>2376</v>
+        <v>2368</v>
       </c>
       <c r="K16" t="s">
-        <v>2377</v>
+        <v>2369</v>
       </c>
       <c r="L16" t="s">
-        <v>2376</v>
+        <v>2368</v>
       </c>
       <c r="M16" t="s">
-        <v>2367</v>
+        <v>2359</v>
       </c>
       <c r="N16" t="s">
-        <v>2334</v>
+        <v>2326</v>
       </c>
       <c r="O16"/>
       <c r="P16" t="n">
@@ -11935,33 +11790,33 @@
         <v>1518</v>
       </c>
       <c r="E17" t="s">
-        <v>2335</v>
+        <v>2327</v>
       </c>
       <c r="F17" t="s">
-        <v>2330</v>
+        <v>2322</v>
       </c>
       <c r="G17" t="s">
-        <v>2328</v>
+        <v>2320</v>
       </c>
       <c r="H17"/>
       <c r="I17"/>
       <c r="J17" t="s">
-        <v>2378</v>
+        <v>2370</v>
       </c>
       <c r="K17" t="s">
-        <v>2379</v>
+        <v>2371</v>
       </c>
       <c r="L17" t="s">
-        <v>2378</v>
+        <v>2370</v>
       </c>
       <c r="M17" t="s">
-        <v>2380</v>
+        <v>2372</v>
       </c>
       <c r="N17" t="s">
-        <v>2338</v>
+        <v>2330</v>
       </c>
       <c r="O17" t="s">
-        <v>2381</v>
+        <v>2373</v>
       </c>
       <c r="P17" t="n">
         <v>33092</v>
@@ -11981,33 +11836,33 @@
         <v>3405</v>
       </c>
       <c r="E18" t="s">
-        <v>2335</v>
+        <v>2327</v>
       </c>
       <c r="F18" t="s">
-        <v>2330</v>
+        <v>2322</v>
       </c>
       <c r="G18" t="s">
-        <v>2328</v>
+        <v>2320</v>
       </c>
       <c r="H18"/>
       <c r="I18"/>
       <c r="J18" t="s">
-        <v>2382</v>
+        <v>2374</v>
       </c>
       <c r="K18" t="s">
-        <v>2383</v>
+        <v>2375</v>
       </c>
       <c r="L18" t="s">
-        <v>2382</v>
+        <v>2374</v>
       </c>
       <c r="M18" t="s">
-        <v>2384</v>
+        <v>2376</v>
       </c>
       <c r="N18" t="s">
-        <v>2338</v>
+        <v>2330</v>
       </c>
       <c r="O18" t="s">
-        <v>2385</v>
+        <v>2377</v>
       </c>
       <c r="P18" t="n">
         <v>35945</v>
@@ -12027,33 +11882,33 @@
         <v>1629</v>
       </c>
       <c r="E19" t="s">
-        <v>2335</v>
+        <v>2327</v>
       </c>
       <c r="F19" t="s">
-        <v>2330</v>
+        <v>2322</v>
       </c>
       <c r="G19" t="s">
-        <v>2328</v>
+        <v>2320</v>
       </c>
       <c r="H19"/>
       <c r="I19"/>
       <c r="J19" t="s">
-        <v>2386</v>
+        <v>2378</v>
       </c>
       <c r="K19" t="s">
-        <v>2387</v>
+        <v>2379</v>
       </c>
       <c r="L19" t="s">
-        <v>2386</v>
+        <v>2378</v>
       </c>
       <c r="M19" t="s">
-        <v>2388</v>
+        <v>2380</v>
       </c>
       <c r="N19" t="s">
-        <v>2338</v>
+        <v>2330</v>
       </c>
       <c r="O19" t="s">
-        <v>2389</v>
+        <v>2381</v>
       </c>
       <c r="P19" t="n">
         <v>39010</v>
@@ -12073,33 +11928,33 @@
         <v>1608</v>
       </c>
       <c r="E20" t="s">
-        <v>2329</v>
+        <v>2321</v>
       </c>
       <c r="F20" t="s">
-        <v>2330</v>
+        <v>2322</v>
       </c>
       <c r="G20" t="s">
-        <v>2328</v>
+        <v>2320</v>
       </c>
       <c r="H20"/>
       <c r="I20"/>
       <c r="J20" t="s">
-        <v>2390</v>
+        <v>2382</v>
       </c>
       <c r="K20" t="s">
-        <v>2391</v>
+        <v>2383</v>
       </c>
       <c r="L20" t="s">
-        <v>2390</v>
+        <v>2382</v>
       </c>
       <c r="M20" t="s">
-        <v>2392</v>
+        <v>2384</v>
       </c>
       <c r="N20" t="s">
-        <v>2338</v>
+        <v>2330</v>
       </c>
       <c r="O20" t="s">
-        <v>2393</v>
+        <v>2385</v>
       </c>
       <c r="P20" t="n">
         <v>40990</v>
@@ -12119,33 +11974,33 @@
         <v>1533</v>
       </c>
       <c r="E21" t="s">
-        <v>2329</v>
+        <v>2321</v>
       </c>
       <c r="F21" t="s">
-        <v>2330</v>
+        <v>2322</v>
       </c>
       <c r="G21" t="s">
-        <v>2328</v>
+        <v>2320</v>
       </c>
       <c r="H21"/>
       <c r="I21"/>
       <c r="J21" t="s">
-        <v>2394</v>
+        <v>2386</v>
       </c>
       <c r="K21" t="s">
-        <v>2395</v>
+        <v>2387</v>
       </c>
       <c r="L21" t="s">
-        <v>2394</v>
+        <v>2386</v>
       </c>
       <c r="M21" t="s">
-        <v>2396</v>
+        <v>2388</v>
       </c>
       <c r="N21" t="s">
-        <v>2338</v>
+        <v>2330</v>
       </c>
       <c r="O21" t="s">
-        <v>2397</v>
+        <v>2389</v>
       </c>
       <c r="P21" t="n">
         <v>42809</v>
@@ -12165,33 +12020,33 @@
         <v>747</v>
       </c>
       <c r="E22" t="s">
-        <v>2335</v>
+        <v>2327</v>
       </c>
       <c r="F22" t="s">
-        <v>2330</v>
+        <v>2322</v>
       </c>
       <c r="G22" t="s">
-        <v>2328</v>
+        <v>2320</v>
       </c>
       <c r="H22"/>
       <c r="I22"/>
       <c r="J22" t="s">
-        <v>2398</v>
+        <v>2390</v>
       </c>
       <c r="K22" t="s">
-        <v>2399</v>
+        <v>2391</v>
       </c>
       <c r="L22" t="s">
-        <v>2398</v>
+        <v>2390</v>
       </c>
       <c r="M22" t="s">
-        <v>2400</v>
+        <v>2392</v>
       </c>
       <c r="N22" t="s">
-        <v>2338</v>
+        <v>2330</v>
       </c>
       <c r="O22" t="s">
-        <v>2401</v>
+        <v>2393</v>
       </c>
       <c r="P22" t="n">
         <v>44418</v>
@@ -12211,33 +12066,33 @@
         <v>891</v>
       </c>
       <c r="E23" t="s">
-        <v>2335</v>
+        <v>2327</v>
       </c>
       <c r="F23" t="s">
-        <v>2330</v>
+        <v>2322</v>
       </c>
       <c r="G23" t="s">
-        <v>2328</v>
+        <v>2320</v>
       </c>
       <c r="H23"/>
       <c r="I23"/>
       <c r="J23" t="s">
-        <v>2402</v>
+        <v>2394</v>
       </c>
       <c r="K23" t="s">
-        <v>2403</v>
+        <v>2395</v>
       </c>
       <c r="L23" t="s">
-        <v>2402</v>
+        <v>2394</v>
       </c>
       <c r="M23" t="s">
-        <v>2404</v>
+        <v>2396</v>
       </c>
       <c r="N23" t="s">
-        <v>2338</v>
+        <v>2330</v>
       </c>
       <c r="O23" t="s">
-        <v>2405</v>
+        <v>2397</v>
       </c>
       <c r="P23" t="n">
         <v>45508</v>
@@ -12257,33 +12112,33 @@
         <v>2763</v>
       </c>
       <c r="E24" t="s">
-        <v>2335</v>
+        <v>2327</v>
       </c>
       <c r="F24" t="s">
-        <v>2330</v>
+        <v>2322</v>
       </c>
       <c r="G24" t="s">
-        <v>2328</v>
+        <v>2320</v>
       </c>
       <c r="H24"/>
       <c r="I24"/>
       <c r="J24" t="s">
-        <v>2406</v>
+        <v>2398</v>
       </c>
       <c r="K24" t="s">
-        <v>2407</v>
+        <v>2399</v>
       </c>
       <c r="L24" t="s">
-        <v>2406</v>
+        <v>2398</v>
       </c>
       <c r="M24" t="s">
-        <v>2408</v>
+        <v>2400</v>
       </c>
       <c r="N24" t="s">
-        <v>2338</v>
+        <v>2330</v>
       </c>
       <c r="O24" t="s">
-        <v>2409</v>
+        <v>2401</v>
       </c>
       <c r="P24" t="n">
         <v>48323</v>
@@ -12303,33 +12158,33 @@
         <v>924</v>
       </c>
       <c r="E25" t="s">
-        <v>2329</v>
+        <v>2321</v>
       </c>
       <c r="F25" t="s">
-        <v>2330</v>
+        <v>2322</v>
       </c>
       <c r="G25" t="s">
-        <v>2328</v>
+        <v>2320</v>
       </c>
       <c r="H25"/>
       <c r="I25"/>
       <c r="J25" t="s">
-        <v>2410</v>
+        <v>2402</v>
       </c>
       <c r="K25" t="s">
-        <v>2411</v>
+        <v>2403</v>
       </c>
       <c r="L25" t="s">
-        <v>2410</v>
+        <v>2402</v>
       </c>
       <c r="M25" t="s">
-        <v>2412</v>
+        <v>2404</v>
       </c>
       <c r="N25" t="s">
-        <v>2338</v>
+        <v>2330</v>
       </c>
       <c r="O25" t="s">
-        <v>2413</v>
+        <v>2405</v>
       </c>
       <c r="P25" t="n">
         <v>50492</v>
